--- a/PO_TBD_20260529.xlsx
+++ b/PO_TBD_20260529.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:I148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -694,16 +694,16 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>4.2</v>
+        <v>3.99</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>281.4</v>
+        <v>395.01</v>
       </c>
     </row>
     <row r="13">
@@ -1206,16 +1206,16 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>3.4</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>37.4</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="29">
@@ -1366,16 +1366,16 @@
         </is>
       </c>
       <c r="E33" s="8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G33" s="10" t="n">
         <v>1.62333</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>89.28</v>
+        <v>94.15000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>TAB MUCOSOLVAN (AMBROXOL) 30MG DKSH</t>
+          <t>TAB PANTOPRAZOLE 40MG (GASTRO-RESISTANT) SANDOZ</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -2166,16 +2166,16 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>0.459</v>
+        <v>0.57143</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>58.75</v>
+        <v>65.14</v>
       </c>
     </row>
     <row r="59">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>TAB SPASIL (DIPHENOXYLATE 2.5MG/ATROPINE 0.025MG) IMEKS</t>
+          <t>TAB MUCOSOLVAN (AMBROXOL) 30MG DKSH</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="E59" s="8" t="n">
-        <v>480</v>
+        <v>80</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>0.164</v>
+        <v>0.459</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>33.29</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="60">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>TAB CLARINASE (PSEUDOEPHEDRINE 120MG, LORATADINE 5MG) BAYER</t>
+          <t>TAB SPASIL (DIPHENOXYLATE 2.5MG/ATROPINE 0.025MG) IMEKS</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2230,16 +2230,16 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>1.814</v>
+        <v>0.164</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>304.75</v>
+        <v>33.29</v>
       </c>
     </row>
     <row r="61">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>TABLET METGYL (METRONIDAZOLE) 400MG SM PHARMACEUTICALS</t>
+          <t>TAB CLARINASE (PSEUDOEPHEDRINE 120MG, LORATADINE 5MG) BAYER</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -2262,16 +2262,16 @@
         </is>
       </c>
       <c r="E61" s="8" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>0.089</v>
+        <v>1.814</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>9.43</v>
+        <v>304.75</v>
       </c>
     </row>
     <row r="62">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>TAB NORCOLUT (NORETHISTERONE) 5MG PAHANG PHARMACY</t>
+          <t>TABLET METGYL (METRONIDAZOLE) 400MG SM PHARMACEUTICALS</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -2294,16 +2294,16 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>0.5</v>
+        <v>0.089</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>10.5</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="63">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>TAB VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
+          <t>TAB NORCOLUT (NORETHISTERONE) 5MG PAHANG PHARMACY</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -2326,16 +2326,16 @@
         </is>
       </c>
       <c r="E63" s="8" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>0.119</v>
+        <v>0.5</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>3.21</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="64">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>TAB IBUPROFEN 400MG Y.S.P.</t>
+          <t>TAB VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -2361,13 +2361,13 @@
         <v>90</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>0.203</v>
+        <v>0.119</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>7.71</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="65">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>TAB PONTALON (MEFENAMIC ACID) 500MG Y.S.P.</t>
+          <t>TAB IBUPROFEN 400MG Y.S.P.</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -2390,16 +2390,16 @@
         </is>
       </c>
       <c r="E65" s="8" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>0.143</v>
+        <v>0.203</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>6.43</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="66">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>INJ PIRIMAT (CHLORPHENIRAMINE) 10MG/ML DUOPHARMA</t>
+          <t>TAB PONTALON (MEFENAMIC ACID) 500MG Y.S.P.</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -2418,20 +2418,20 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>1.75</v>
+        <v>0.143</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>19.25</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="67">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>TAB DEXALONE ( DEXAMETHASONE ) 0.5MG DUOPHARMA</t>
+          <t>INJ PIRIMAT (CHLORPHENIRAMINE) 10MG/ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -2450,20 +2450,20 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E67" s="8" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>0.08</v>
+        <v>1.75</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>2.8</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="68">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>TAB DUOFOLIC (FOLIC ACID) 5MG DUOPHARMA</t>
+          <t>TAB DEXALONE ( DEXAMETHASONE ) 0.5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -2486,16 +2486,16 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>0.065</v>
+        <v>0.08</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>1.69</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="69">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
+          <t>TAB DUOFOLIC (FOLIC ACID) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -2518,16 +2518,16 @@
         </is>
       </c>
       <c r="E69" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>0.584</v>
+        <v>0.065</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>21.02</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="70">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>CAP LOMODIUM (LOPERAMIDE) 2MG DYNAPHARM</t>
+          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -2550,16 +2550,16 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>0.093</v>
+        <v>0.584</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>1.49</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="71">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
+          <t>CAP LOMODIUM (LOPERAMIDE) 2MG DYNAPHARM</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -2578,20 +2578,20 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E71" s="8" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="72">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>TAB DUPHASTON (DYDROGESTERONE) 10MG ABBOTT</t>
+          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -2610,20 +2610,20 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>3.675</v>
+        <v>0</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>62.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>SYR PREDSOLONE (PREDNISOLONE 2.5MG/5ML) 100ML DYNAPHARM</t>
+          <t>TAB DUPHASTON (DYDROGESTERONE) 10MG ABBOTT</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -2642,20 +2642,20 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E73" s="8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>0</v>
+        <v>3.675</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>0</v>
+        <v>62.47</v>
       </c>
     </row>
     <row r="74">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>TAB HOVASC (AMLODIPINE) 5MG HOVID</t>
+          <t>SYR PREDSOLONE (PREDNISOLONE 2.5MG/5ML) 100ML DYNAPHARM</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -2674,20 +2674,20 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>TAB HOVASC (AMLODIPINE) 10MG HOVID</t>
+          <t>TAB HOVASC (AMLODIPINE) 5MG HOVID</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -2710,16 +2710,16 @@
         </is>
       </c>
       <c r="E75" s="8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>3.5</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="76">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>TAB NORMATEN (ATENOLOL) 50MG XEPA</t>
+          <t>TAB HOVASC (AMLODIPINE) 10MG HOVID</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -2742,16 +2742,16 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>0.26786</v>
+        <v>0.35</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="77">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>TAB DELTACARBON (CHARCOAL) 250MG IMEKS</t>
+          <t>TAB NORMATEN (ATENOLOL) 50MG XEPA</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -2774,16 +2774,16 @@
         </is>
       </c>
       <c r="E77" s="8" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>0.438</v>
+        <v>0.26786</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>6.57</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="78">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
+          <t>TAB DELTACARBON (CHARCOAL) 250MG IMEKS</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -2806,16 +2806,16 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>1.617</v>
+        <v>0.438</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>25.87</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="79">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>TAB COPASTIN (CLOPERASTINE) 10MG Y.S.P.</t>
+          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -2838,16 +2838,16 @@
         </is>
       </c>
       <c r="E79" s="8" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>0.236</v>
+        <v>1.617</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>6.84</v>
+        <v>25.87</v>
       </c>
     </row>
     <row r="80">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
+          <t>TAB COPASTIN (CLOPERASTINE) 10MG Y.S.P.</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>1.53</v>
+        <v>0.236</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>15.3</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="81">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>SMECTA (DIOSMECTITE 3G) ORANGE-VANILLA POWDER SACHETS ZUELLIG</t>
+          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -2898,20 +2898,20 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>SACHET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E81" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>19.92</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="82">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>TAB CAFFOX ( ERGOTAMINE TARTRATE 1MG + CAFFINE 100MG ) IMEKS</t>
+          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -2930,20 +2930,20 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>0.73</v>
+        <v>5.9</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>10.22</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
+          <t>SMECTA (DIOSMECTITE 3G) ORANGE-VANILLA POWDER SACHETS ZUELLIG</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
@@ -2962,20 +2962,20 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>SACHET</t>
         </is>
       </c>
       <c r="E83" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G83" s="10" t="n">
-        <v>1.06</v>
+        <v>1.66</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>14.84</v>
+        <v>19.92</v>
       </c>
     </row>
     <row r="84">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>TAB LORADINE (LORATIDINE)10MG Y.S.P.</t>
+          <t>TAB CAFFOX ( ERGOTAMINE TARTRATE 1MG + CAFFINE 100MG ) IMEKS</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -2998,16 +2998,16 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>0.232</v>
+        <v>0.73</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>4.87</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="85">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>TAB NUELIN SR (THEOPHYLLINE) 250MG INOVA</t>
+          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
@@ -3030,16 +3030,16 @@
         </is>
       </c>
       <c r="E85" s="8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F85" s="8" t="n">
         <v>14</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>0.78</v>
+        <v>1.06</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>10.92</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="86">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>TAB DULCOLAX ( BISACODYL ) 5MG SANOFI</t>
+          <t>TAB LORADINE (LORATIDINE)10MG Y.S.P.</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -3062,16 +3062,16 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>0.265</v>
+        <v>0.232</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>3.98</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="87">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
+          <t>TAB NUELIN SR (THEOPHYLLINE) 250MG INOVA</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
@@ -3097,13 +3097,13 @@
         <v>20</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>27.88</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="88">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
+          <t>TAB DULCOLAX ( BISACODYL ) 5MG SANOFI</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -3126,16 +3126,16 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>1.44</v>
+        <v>0.265</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>14.4</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="89">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>TAB ZITHROLIDE (AZITHROMYCIN)  500MG PHARMANIAGA</t>
+          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -3154,20 +3154,20 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E89" s="8" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>5.5</v>
+        <v>0.68</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>27.5</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="90">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>NEBULE VENTOLIN (SALBUTAMOL) 2.5MG/2.5ML GSK</t>
+          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -3186,20 +3186,20 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>RESPULE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>4.82</v>
+        <v>1.44</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>24.1</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="91">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>TAB ZITHROMAX (AZITHROMYCIN) 250MG 6'S PFIZER</t>
+          <t>TAB ZITHROLIDE (AZITHROMYCIN)  500MG PHARMANIAGA</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
@@ -3222,16 +3222,16 @@
         </is>
       </c>
       <c r="E91" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G91" s="10" t="n">
-        <v>42.4</v>
+        <v>5.5</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>84.8</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="92">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>SUPP VOREN (DICLOFENAC SODIUM) 25MG Y.S.P.</t>
+          <t>NEBULE VENTOLIN (SALBUTAMOL) 2.5MG/2.5ML GSK</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -3250,20 +3250,20 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>SUPPOSITORIES</t>
+          <t>RESPULE</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>1.66</v>
+        <v>4.82</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>6.64</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="93">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>SUPP VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
+          <t>TAB ZITHROMAX (AZITHROMYCIN) 250MG 6'S PFIZER</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
@@ -3282,20 +3282,20 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>SUPPOSITORIES</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E93" s="8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" s="10" t="n">
-        <v>1.59</v>
+        <v>42.4</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>1.59</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="94">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>CAP BIOZOLE (FLUCANAZOLE) 150MG MEDISPEC</t>
+          <t>SUPP VOREN (DICLOFENAC SODIUM) 25MG Y.S.P.</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -3314,20 +3314,20 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>SUPPOSITORIES</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>4.91</v>
+        <v>1.66</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>24.55</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="95">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>CANDID-B ( CLOTRIMAZOLE 1%W/W /BECLOMETHASONE 0.025%W/W ) CREAM 15G Y.S.P.</t>
+          <t>SUPP VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -3346,20 +3346,20 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>SUPPOSITORIES</t>
         </is>
       </c>
       <c r="E95" s="8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F95" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G95" s="10" t="n">
-        <v>12.33</v>
+        <v>1.59</v>
       </c>
       <c r="H95" s="10" t="n">
-        <v>12.33</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="96">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>CANDID EARDROPS (CLOTRIMAZOLE 1%) 15ML GLENMARK</t>
+          <t>CAP BIOZOLE (FLUCANAZOLE) 150MG MEDISPEC</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -3378,20 +3378,20 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>18.95</v>
+        <v>4.91</v>
       </c>
       <c r="H96" s="7" t="n">
-        <v>18.95</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="97">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>INJ METHYCOBAL (MECOBALAMIN B12) 500MCG 1ML VIAL EISAI</t>
+          <t>CANDID-B ( CLOTRIMAZOLE 1%W/W /BECLOMETHASONE 0.025%W/W ) CREAM 15G Y.S.P.</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
@@ -3410,20 +3410,20 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E97" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F97" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G97" s="10" t="n">
-        <v>6.8</v>
+        <v>12.33</v>
       </c>
       <c r="H97" s="10" t="n">
-        <v>13.6</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="98">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>SYR LACTUL (LACTULOSE 670MG/ML) 100ML Y.S.P.</t>
+          <t>CANDID EARDROPS (CLOTRIMAZOLE 1%) 15ML GLENMARK</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -3446,16 +3446,16 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>10</v>
+        <v>18.95</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>20</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="99">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>SYR COLIMIX (DICYCLOMINE 5MG/ SIMETHICONE 50MG) 90ML XEPA</t>
+          <t>INJ METHYCOBAL (MECOBALAMIN B12) 500MCG 1ML VIAL EISAI</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
@@ -3474,20 +3474,20 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E99" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F99" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G99" s="10" t="n">
-        <v>7.55</v>
+        <v>6.8</v>
       </c>
       <c r="H99" s="10" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="100">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>MDI VENTOLIN EVOHALER (SALBUTAMOL 100MCG) GSK</t>
+          <t>SYR LACTUL (LACTULOSE 670MG/ML) 100ML Y.S.P.</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -3506,20 +3506,20 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F100" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>26.1</v>
+        <v>10</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>52.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>INJ SHINCORT (TRIAMCINOLONE ACETONIDE 40MG/ML) 1ML VIAL Y.S.P.</t>
+          <t>SYR COLIMIX (DICYCLOMINE 5MG/ SIMETHICONE 50MG) 90ML XEPA</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
@@ -3538,20 +3538,20 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E101" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F101" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G101" s="10" t="n">
-        <v>8.15</v>
+        <v>7.55</v>
       </c>
       <c r="H101" s="10" t="n">
-        <v>40.75</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="102">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>SYR FUCON (HYOSCINE-N-BUTYLBROMIDE) 1MG/ML 60ML Y.S.P.</t>
+          <t>MDI VENTOLIN EVOHALER (SALBUTAMOL 100MCG) GSK</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -3570,20 +3570,20 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F102" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>7.05</v>
+        <v>26.1</v>
       </c>
       <c r="H102" s="7" t="n">
-        <v>14.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="103">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>NASAL DROPS ILIADIN 0.01% (OXYMETHAZOLINE) DECONGESTANT (&lt; 12MTHS ) P&amp;G</t>
+          <t>INJ SHINCORT (TRIAMCINOLONE ACETONIDE 40MG/ML) 1ML VIAL Y.S.P.</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
@@ -3602,20 +3602,20 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E103" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F103" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G103" s="10" t="n">
-        <v>16.56</v>
+        <v>8.15</v>
       </c>
       <c r="H103" s="10" t="n">
-        <v>33.12</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="104">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>DIFFLAM FORTE THROAT SPRAY  (BENZYDAMINE 0.3% W/V) ADULTS &amp; CHILD (&gt;6YRS) INOVA</t>
+          <t>SYR FUCON (HYOSCINE-N-BUTYLBROMIDE) 1MG/ML 60ML Y.S.P.</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -3638,16 +3638,16 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>32</v>
+        <v>7.05</v>
       </c>
       <c r="H104" s="7" t="n">
-        <v>128</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="105">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>EYE/EAR DROPS DEXTRACIN (DEXAMETHASONE &amp; NEOMYCIN) XEPA</t>
+          <t>NASAL DROPS ILIADIN 0.01% (OXYMETHAZOLINE) DECONGESTANT (&lt; 12MTHS ) P&amp;G</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
@@ -3670,16 +3670,16 @@
         </is>
       </c>
       <c r="E105" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F105" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G105" s="10" t="n">
-        <v>5</v>
+        <v>16.56</v>
       </c>
       <c r="H105" s="10" t="n">
-        <v>20</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="106">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>INJ NON-PREG (MEDROXYPROGESTERONE ACETATE IM 150MG/3ML) VIAL HEALOL PHARMA</t>
+          <t>DIFFLAM FORTE THROAT SPRAY  (BENZYDAMINE 0.3% W/V) ADULTS &amp; CHILD (&gt;6YRS) INOVA</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -3698,20 +3698,20 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="H106" s="7" t="n">
-        <v>8.800000000000001</v>
+        <v>128</v>
       </c>
     </row>
     <row r="107">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>TAB ESCAPELLE (LEVONORGESTREL) 1.5MG 1'S PAHANG PHARMACY</t>
+          <t>EYE/EAR DROPS DEXTRACIN (DEXAMETHASONE &amp; NEOMYCIN) XEPA</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
@@ -3730,20 +3730,20 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E107" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F107" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F107" s="8" t="n">
-        <v>2</v>
-      </c>
       <c r="G107" s="10" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="H107" s="10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>TAB SYNFLEX (NAPROXEN SODIUM) 550MG DKSH</t>
+          <t>INJ NON-PREG (MEDROXYPROGESTERONE ACETATE IM 150MG/3ML) VIAL HEALOL PHARMA</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -3762,20 +3762,20 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>1.414</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H108" s="7" t="n">
-        <v>7.07</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="109">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
+          <t>TAB ESCAPELLE (LEVONORGESTREL) 1.5MG 1'S PAHANG PHARMACY</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
@@ -3794,20 +3794,20 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E109" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F109" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F109" s="8" t="n">
-        <v>4</v>
-      </c>
       <c r="G109" s="10" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="H109" s="10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="110">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>VOREN (DICLOFENAC SODIUM 1%W/W) GEL PLUS 20G Y.SP.</t>
+          <t>TAB SYNFLEX (NAPROXEN SODIUM) 550MG DKSH</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
@@ -3826,20 +3826,20 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>9</v>
+        <v>1.414</v>
       </c>
       <c r="H110" s="7" t="n">
-        <v>27</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="111">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
+          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
@@ -3858,20 +3858,20 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E111" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G111" s="10" t="n">
-        <v>9.65</v>
+        <v>5.5</v>
       </c>
       <c r="H111" s="10" t="n">
-        <v>19.3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>EFFERVESCENT ACETYLCYSTIENE (N-ACETYLCYSTIENE) 600MG 2'S SANDOZ</t>
+          <t>VOREN (DICLOFENAC SODIUM 1%W/W) GEL PLUS 20G Y.SP.</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -3890,20 +3890,20 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>STRIP</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G112" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="F112" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G112" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="H112" s="7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
+          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
@@ -3922,20 +3922,20 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E113" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G113" s="10" t="n">
-        <v>5.9</v>
+        <v>9.65</v>
       </c>
       <c r="H113" s="10" t="n">
-        <v>59</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="114">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>CHAMPS D-WORMS SUSPENSION (ALBENDAZOLE 200MG/5ML) 10ML DUOPHARMA</t>
+          <t>EFFERVESCENT ACETYLCYSTIENE (N-ACETYLCYSTIENE) 600MG 2'S SANDOZ</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -3954,20 +3954,20 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>STRIP</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G114" s="7" t="n">
-        <v>9.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="H114" s="7" t="n">
-        <v>9.449999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>TAB DAFLON (DIOSMIN 900MG, HESPERIDIN 100MG) 1000MG SERVIER</t>
+          <t>CHAMPS D-WORMS SUSPENSION (ALBENDAZOLE 200MG/5ML) 10ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
@@ -3986,20 +3986,20 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E115" s="8" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G115" s="10" t="n">
-        <v>2.93</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H115" s="10" t="n">
-        <v>14.65</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="116">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>FOBAN CREAM (FUSIDIC ACID 2% W/W) 15G HOE</t>
+          <t>TAB DAFLON (DIOSMIN 900MG, HESPERIDIN 100MG) 1000MG SERVIER</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -4018,20 +4018,20 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G116" s="7" t="n">
-        <v>14.3</v>
+        <v>2.93</v>
       </c>
       <c r="H116" s="7" t="n">
-        <v>14.3</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="117">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>PROCTOSEDYL OINTMENT (FRAMYCETIN SULPHATE 1% W/W, HYDROCORTISONE 0.5% W/W, CINCHOCAINE.5% W/W, AESCULIN 1% W/W) 15G ZUELLIG PHARMA</t>
+          <t>FOBAN CREAM (FUSIDIC ACID 2% W/W) 15G HOE</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
@@ -4054,16 +4054,16 @@
         </is>
       </c>
       <c r="E117" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G117" s="10" t="n">
-        <v>35</v>
+        <v>14.3</v>
       </c>
       <c r="H117" s="10" t="n">
-        <v>35</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="118">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>ELLGY CORNS &amp; WARTS  (SALICYLIC ACID 17% W/V) 10ML HOE</t>
+          <t>PROCTOSEDYL OINTMENT (FRAMYCETIN SULPHATE 1% W/W, HYDROCORTISONE 0.5% W/W, CINCHOCAINE.5% W/W, AESCULIN 1% W/W) 15G ZUELLIG PHARMA</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -4086,16 +4086,16 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G118" s="7" t="n">
-        <v>14.93</v>
+        <v>35</v>
       </c>
       <c r="H118" s="7" t="n">
-        <v>29.86</v>
+        <v>35</v>
       </c>
     </row>
     <row r="119">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>FOBANCORT CREAM (FUSIDIC ACID 2% W/W, BETAMETHASONE 0.05% W/W) 15G HOE</t>
+          <t>ELLGY CORNS &amp; WARTS  (SALICYLIC ACID 17% W/V) 10ML HOE</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
@@ -4118,16 +4118,16 @@
         </is>
       </c>
       <c r="E119" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F119" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F119" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="G119" s="10" t="n">
-        <v>14.3</v>
+        <v>14.93</v>
       </c>
       <c r="H119" s="10" t="n">
-        <v>14.3</v>
+        <v>29.86</v>
       </c>
     </row>
     <row r="120">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>DYFAZINE CREAM (SILVER SULPHADIAZINE 1%) 50G DYNAPHARM</t>
+          <t>FOBANCORT CREAM (FUSIDIC ACID 2% W/W, BETAMETHASONE 0.05% W/W) 15G HOE</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -4150,16 +4150,16 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>13.64</v>
+        <v>14.3</v>
       </c>
       <c r="H120" s="7" t="n">
-        <v>13.64</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="121">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>INJ LARTIL (PROCHLORPERAZINE MESYLATE)12.5MG/ML 1ML VIAL DUOPHARMA</t>
+          <t>DYFAZINE CREAM (SILVER SULPHADIAZINE 1%) 50G DYNAPHARM</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
@@ -4178,20 +4178,20 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E121" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F121" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G121" s="10" t="n">
-        <v>3.48</v>
+        <v>13.64</v>
       </c>
       <c r="H121" s="10" t="n">
-        <v>6.96</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="122">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>CERUMOL EAR WAX SOFTNER DROPS 10ML</t>
+          <t>INJ LARTIL (PROCHLORPERAZINE MESYLATE)12.5MG/ML 1ML VIAL DUOPHARMA</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -4220,10 +4220,10 @@
         <v>2</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>15</v>
+        <v>3.48</v>
       </c>
       <c r="H122" s="7" t="n">
-        <v>30</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="123">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>CIPMAX (CIPROFLOXACIN 0.3%) EYE DROPS 5ML SAMCHUNDANG</t>
+          <t>CERUMOL EAR WAX SOFTNER DROPS 10ML</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
@@ -4246,16 +4246,16 @@
         </is>
       </c>
       <c r="E123" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G123" s="10" t="n">
-        <v>9.5</v>
+        <v>15</v>
       </c>
       <c r="H123" s="10" t="n">
-        <v>28.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>KEZORAL (KETOCONAZOLE 2% W/W) CREAM 15G DUOPHARMA</t>
+          <t>CIPMAX (CIPROFLOXACIN 0.3%) EYE DROPS 5ML SAMCHUNDANG</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -4274,20 +4274,20 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F124" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
       <c r="H124" s="7" t="n">
-        <v>23.1</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="125">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>VICIDE CREAM 5%  (ACYCLOVIR 15MG/G) 10G PAHANG</t>
+          <t>KEZORAL (KETOCONAZOLE 2% W/W) CREAM 15G DUOPHARMA</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
@@ -4310,16 +4310,16 @@
         </is>
       </c>
       <c r="E125" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G125" s="10" t="n">
-        <v>7.45</v>
+        <v>7.7</v>
       </c>
       <c r="H125" s="10" t="n">
-        <v>7.45</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="126">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>APPETON MV LYSINE SYRUP 120ML (VITAMIN A 1000IU + VITAMIN D3 200IU + VITAMIN B1 0.5MG + VITAMIN B2 0.5MG + VITAMIN B6 0.5MG + VITAMIN E 5IU + NICOTINAMIDE 6MG + PANTOTHENIC ACID 2MG + LYSINE 80MG) KOTRA PHARMA</t>
+          <t>VICIDE CREAM 5%  (ACYCLOVIR 15MG/G) 10G PAHANG</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
@@ -4338,20 +4338,20 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G126" s="7" t="n">
-        <v>39.04</v>
+        <v>7.45</v>
       </c>
       <c r="H126" s="7" t="n">
-        <v>39.04</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="127">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>AEVA THYMOL GARGLE 120ML APEX</t>
+          <t>APPETON MV LYSINE SYRUP 120ML (VITAMIN A 1000IU + VITAMIN D3 200IU + VITAMIN B1 0.5MG + VITAMIN B2 0.5MG + VITAMIN B6 0.5MG + VITAMIN E 5IU + NICOTINAMIDE 6MG + PANTOTHENIC ACID 2MG + LYSINE 80MG) KOTRA PHARMA</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
@@ -4374,16 +4374,16 @@
         </is>
       </c>
       <c r="E127" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F127" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G127" s="10" t="n">
-        <v>5.3</v>
+        <v>39.04</v>
       </c>
       <c r="H127" s="10" t="n">
-        <v>10.6</v>
+        <v>39.04</v>
       </c>
     </row>
     <row r="128">
@@ -4392,30 +4392,30 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>SUPP DIMENHYDRINATE 50MG DRIMINATE Y.S.P</t>
+          <t>AEVA THYMOL GARGLE 120ML APEX</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>DRIMINATE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>SUPPOSITORIES</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F128" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G128" s="7" t="n">
-        <v>1.29</v>
+        <v>5.3</v>
       </c>
       <c r="H128" s="7" t="n">
-        <v>2.58</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="129">
@@ -4424,30 +4424,30 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>KLORAXIN EYE OINTMENT ( CHLORAMPHENICOL 1%) 5G UNIMED</t>
+          <t>SUPP DIMENHYDRINATE 50MG DRIMINATE Y.S.P</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DRIMINATE</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>SUPPOSITORIES</t>
         </is>
       </c>
       <c r="E129" s="8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F129" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G129" s="10" t="n">
-        <v>2.8</v>
+        <v>1.29</v>
       </c>
       <c r="H129" s="10" t="n">
-        <v>5.6</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="130">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>INJ TT VACCINE (TETANUS) 0.5ML SM PHARMA</t>
+          <t>KLORAXIN EYE OINTMENT ( CHLORAMPHENICOL 1%) 5G UNIMED</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
@@ -4466,20 +4466,20 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>0.5ML</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="H130" s="7" t="n">
-        <v>26.25</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="131">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>INJ TYPHIM IV ( TYPHOID VACCINE ) SANOFI</t>
+          <t>INJ TT VACCINE (TETANUS) 0.5ML SM PHARMA</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
@@ -4498,20 +4498,20 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>0.5ML</t>
         </is>
       </c>
       <c r="E131" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F131" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G131" s="10" t="n">
-        <v>59</v>
+        <v>3.75</v>
       </c>
       <c r="H131" s="10" t="n">
-        <v>118</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="132">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>IBUFEN SYRUP (IBUPROFEN 100MG/ 5ML) DYNAPHARM</t>
+          <t>INJ TYPHIM IV ( TYPHOID VACCINE ) SANOFI</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -4530,20 +4530,20 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>BTL</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F132" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G132" s="7" t="n">
-        <v>3.27</v>
+        <v>59</v>
       </c>
       <c r="H132" s="7" t="n">
-        <v>6.54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="133">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>INJ PRIORIX (MMR) 0.5ML GSK</t>
+          <t>IBUFEN SYRUP (IBUPROFEN 100MG/ 5ML) DYNAPHARM</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
@@ -4562,20 +4562,20 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>BTL</t>
         </is>
       </c>
       <c r="E133" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G133" s="10" t="n">
-        <v>46.7</v>
+        <v>3.27</v>
       </c>
       <c r="H133" s="10" t="n">
-        <v>46.7</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="134">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>SYR ENHANCIN (AMOXYCILLIN AND CLAVULANIC ACID 312.5MG/5ML ) 60ML RANBAXY</t>
+          <t>INJ PRIORIX (MMR) 0.5ML GSK</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
@@ -4594,20 +4594,20 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G134" s="7" t="n">
-        <v>8.4</v>
+        <v>46.7</v>
       </c>
       <c r="H134" s="7" t="n">
-        <v>16.8</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="135">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>INJ PREDON INJECTION 25MG/ML HEALOL PHARMACEUTICALS SDN. BHD.</t>
+          <t>SYR ENHANCIN (AMOXYCILLIN AND CLAVULANIC ACID 312.5MG/5ML ) 60ML RANBAXY</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
@@ -4626,20 +4626,20 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E135" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F135" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G135" s="10" t="n">
-        <v>1.32</v>
+        <v>8.4</v>
       </c>
       <c r="H135" s="10" t="n">
-        <v>1.32</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="136">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>SYR IXIME ( CEFIXIME 100MG/5ML ) 50ML LUPIN</t>
+          <t>INJ PREDON INJECTION 25MG/ML HEALOL PHARMACEUTICALS SDN. BHD.</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
@@ -4658,20 +4658,20 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G136" s="7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="H136" s="7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="137">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>XOIN (N-BUTYL-2-CYANOACRYLATE) TOPICAL SKIN ADHESIVE 0.25ML REEVAX PHARMA</t>
+          <t>SYR IXIME ( CEFIXIME 100MG/5ML ) 50ML LUPIN</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
@@ -4690,20 +4690,20 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>PEN</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E137" s="8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F137" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G137" s="10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H137" s="10" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>MONITAZONE (MOMETASONE FUROATE) 50MCG/ACTUATION NASAL SPRAY 140MD SHAMCHUNDANG PHARM</t>
+          <t>XOIN (N-BUTYL-2-CYANOACRYLATE) TOPICAL SKIN ADHESIVE 0.25ML REEVAX PHARMA</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
@@ -4722,20 +4722,20 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>PEN</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F138" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G138" s="7" t="n">
-        <v>35.71429</v>
+        <v>30</v>
       </c>
       <c r="H138" s="7" t="n">
-        <v>71.43000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="139">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>APPETON A-Z VITAMIN C 30MG PASTILLES 5'S</t>
+          <t>MONITAZONE (MOMETASONE FUROATE) 50MCG/ACTUATION NASAL SPRAY 140MD SHAMCHUNDANG PHARM</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
@@ -4754,20 +4754,20 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E139" s="8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G139" s="10" t="n">
-        <v>0</v>
+        <v>35.71429</v>
       </c>
       <c r="H139" s="10" t="n">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
     </row>
     <row r="140">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>INJ GARASENT (GENTAMICIN SULPHATE  80MG/2ML AMP) DUOPHARMA</t>
+          <t>APPETON A-Z VITAMIN C 30MG PASTILLES 5'S</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
@@ -4786,20 +4786,20 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>AMPULE</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F140" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F140" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="G140" s="7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H140" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+          <t>INJ GARASENT (GENTAMICIN SULPHATE  80MG/2ML AMP) DUOPHARMA</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
@@ -4822,16 +4822,16 @@
         </is>
       </c>
       <c r="E141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F141" s="8" t="n">
+      <c r="G141" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H141" s="10" t="n">
         <v>3</v>
-      </c>
-      <c r="G141" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H141" s="10" t="n">
-        <v>7.5</v>
       </c>
     </row>
     <row r="142">
@@ -4840,58 +4840,90 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
+          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>AMPULE</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G142" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H142" s="7" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="n">
+        <v>134</v>
+      </c>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
           <t>KETOTOP PLASTER (KETOPROFEN) 30MG 7'S HANDOK</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
         <is>
           <t>PACKET</t>
         </is>
       </c>
-      <c r="E142" s="5" t="n">
+      <c r="E143" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="F142" s="5" t="n">
+      <c r="F143" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G142" s="7" t="n">
+      <c r="G143" s="10" t="n">
         <v>9.021000000000001</v>
       </c>
-      <c r="H142" s="7" t="n">
+      <c r="H143" s="10" t="n">
         <v>9.02</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="11" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="11" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="H143" s="12" t="n">
-        <v>7208.540000000002</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Total line items: 133</t>
-        </is>
+      <c r="H144" s="12" t="n">
+        <v>7401.460000000002</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-29 08:03</t>
+          <t>Total line items: 134</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="13" t="inlineStr">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Generated: 2026-05-29 18:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="inlineStr">
         <is>
           <t>Note: Unit costs are from latest purchase price. Verify with supplier before confirming order.</t>
         </is>
@@ -4899,7 +4931,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A143:G143"/>
+    <mergeCell ref="A144:G144"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
